--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484264_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484264_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1662</v>
+        <v>3.1972</v>
       </c>
       <c r="E2" t="n">
-        <v>2.5027</v>
+        <v>2.8061</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6635</v>
+        <v>0.3911</v>
       </c>
       <c r="G2" t="n">
         <v>3.1816</v>
@@ -610,13 +610,13 @@
         <v>1.3674</v>
       </c>
       <c r="S2" t="n">
-        <v>0.2888</v>
+        <v>0.3198</v>
       </c>
       <c r="T2" t="n">
-        <v>0.3385</v>
+        <v>0.6419</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0497</v>
+        <v>-0.322</v>
       </c>
       <c r="V2" t="n">
         <v>-0.4996</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.4477</v>
+        <v>2.4888</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8362</v>
+        <v>2.7956</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.3885</v>
+        <v>-0.3068</v>
       </c>
       <c r="G3" t="n">
         <v>0.9478</v>
@@ -688,13 +688,13 @@
         <v>1.3674</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.383</v>
+        <v>-0.3418</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.0246</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3583</v>
+        <v>-0.2766</v>
       </c>
       <c r="V3" t="n">
         <v>1.8828</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7246</v>
+        <v>1.2713</v>
       </c>
       <c r="E4" t="n">
-        <v>3.0285</v>
+        <v>3.4935</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.3039</v>
+        <v>-2.2222</v>
       </c>
       <c r="G4" t="n">
         <v>0.8207</v>
@@ -766,13 +766,13 @@
         <v>1.7581</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.3267</v>
+        <v>-0.78</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7592</v>
+        <v>-0.2943</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.5675</v>
+        <v>-0.4858</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3321</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>E. MARTÍN GASCÓN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.3953</v>
+        <v>-0.9655</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0949</v>
+        <v>-0.7673</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.3004</v>
+        <v>-0.1981</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.5712</v>
+        <v>-2.3002</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.8665</v>
+        <v>0.2215</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2953</v>
+        <v>-2.5217</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5099</v>
+        <v>-0.9969</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.6706</v>
+        <v>0.9849</v>
       </c>
       <c r="L5" t="n">
-        <v>1.1607</v>
+        <v>-1.9818</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.0613</v>
+        <v>-1.3032</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.196</v>
+        <v>-0.7634</v>
       </c>
       <c r="O5" t="n">
-        <v>0.1346</v>
+        <v>-0.5399</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9534</v>
+        <v>-1.1721</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S5" t="n">
-        <v>1.8754</v>
+        <v>-0.216</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0912</v>
+        <v>0.183</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2158</v>
+        <v>-0.399</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2772</v>
+        <v>1.5507</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>1.2186</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.5237</v>
+        <v>-2.6989</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.4345</v>
+        <v>-1.2</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0892</v>
+        <v>-1.499</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.3002</v>
+        <v>-2.0208</v>
       </c>
       <c r="H6" t="n">
-        <v>0.2215</v>
+        <v>-1.252</v>
       </c>
       <c r="I6" t="n">
-        <v>-2.5217</v>
+        <v>-0.7688</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.9969</v>
+        <v>-0.8575</v>
       </c>
       <c r="K6" t="n">
-        <v>0.9849</v>
+        <v>-0.2239</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9818</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.3032</v>
+        <v>-1.1634</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.7634</v>
+        <v>-1.0281</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.5399</v>
+        <v>-0.1352</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.586</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R6" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7743</v>
+        <v>0.5173</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4842</v>
+        <v>0.8296</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2901</v>
+        <v>-0.3123</v>
       </c>
       <c r="V6" t="n">
-        <v>1.5507</v>
+        <v>-0.6093</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0.3321</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.2889</v>
+        <v>-2.7238</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.6538</v>
+        <v>-0.4923</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.6351</v>
+        <v>-2.2315</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.0208</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.252</v>
+        <v>1.8286</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.7688</v>
+        <v>-2.3462</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8575</v>
+        <v>0.6603</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.2239</v>
+        <v>3.2758</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-2.6155</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1634</v>
+        <v>-1.1779</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.0281</v>
+        <v>-1.4472</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1352</v>
+        <v>0.2692</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R7" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9273</v>
+        <v>-1.0228</v>
       </c>
       <c r="T7" t="n">
-        <v>1.3757</v>
+        <v>-0.6252</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4485</v>
+        <v>-0.3977</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6093</v>
+        <v>-2.16</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6093</v>
+        <v>-1.8279</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.076</v>
+        <v>-3.1221</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6539</v>
+        <v>-1.7128</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.4221</v>
+        <v>-1.4094</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-2.5712</v>
       </c>
       <c r="H8" t="n">
-        <v>1.8286</v>
+        <v>-3.8665</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.3462</v>
+        <v>1.2953</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6603</v>
+        <v>-0.5099</v>
       </c>
       <c r="K8" t="n">
-        <v>3.2758</v>
+        <v>-1.6706</v>
       </c>
       <c r="L8" t="n">
-        <v>-2.6155</v>
+        <v>1.1607</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.1779</v>
+        <v>-2.0613</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.4472</v>
+        <v>-2.196</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2692</v>
+        <v>0.1346</v>
       </c>
       <c r="P8" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R8" t="n">
         <v>0.9767</v>
       </c>
-      <c r="Q8" t="n">
-        <v>-0.1953</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.1721</v>
-      </c>
       <c r="S8" t="n">
-        <v>-1.3751</v>
+        <v>0.1486</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.7868000000000001</v>
+        <v>0.4733</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.5883</v>
+        <v>-0.3247</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.16</v>
+        <v>0.2772</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3321</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.8279</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.3779</v>
+        <v>-3.1589</v>
       </c>
       <c r="E9" t="n">
-        <v>-3.4203</v>
+        <v>-2.0321</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0423</v>
+        <v>-1.1268</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.8857</v>
+        <v>0.3395</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.9258</v>
+        <v>0.3525</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0401</v>
+        <v>-0.013</v>
       </c>
       <c r="J9" t="n">
-        <v>0.492</v>
+        <v>1.462</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4515</v>
+        <v>2.1489</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0405</v>
+        <v>-0.6869</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3777</v>
+        <v>-1.1225</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3773</v>
+        <v>-1.7964</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0004</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P9" t="n">
-        <v>-2.5395</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q9" t="n">
-        <v>-3.1255</v>
+        <v>-2.9301</v>
       </c>
       <c r="R9" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6169</v>
+        <v>-1.5765</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.7868000000000001</v>
+        <v>-0.5639</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1699</v>
+        <v>-1.0126</v>
       </c>
       <c r="V9" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.9507</v>
+        <v>-3.4826</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.4971</v>
+        <v>-3.1981</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.4536</v>
+        <v>-0.2845</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3395</v>
+        <v>-0.8857</v>
       </c>
       <c r="H10" t="n">
-        <v>0.3525</v>
+        <v>-0.9258</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.013</v>
+        <v>0.0401</v>
       </c>
       <c r="J10" t="n">
-        <v>1.462</v>
+        <v>0.492</v>
       </c>
       <c r="K10" t="n">
-        <v>2.1489</v>
+        <v>0.4515</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6869</v>
+        <v>0.0405</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.1225</v>
+        <v>-1.3777</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.7964</v>
+        <v>-1.3773</v>
       </c>
       <c r="O10" t="n">
-        <v>0.6739000000000001</v>
+        <v>-0.0004</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.3674</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q10" t="n">
-        <v>-2.9301</v>
+        <v>-3.1255</v>
       </c>
       <c r="R10" t="n">
-        <v>1.5627</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.3683</v>
+        <v>-0.7216</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0289</v>
+        <v>-0.5646</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.3394</v>
+        <v>-0.1569</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.5545</v>
+        <v>0.6642</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.5545</v>
+        <v>0.6642</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.349</v>
+        <v>-4.234</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.6083</v>
+        <v>-2.5478</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7406</v>
+        <v>-1.6862</v>
       </c>
       <c r="G11" t="n">
         <v>-1.977</v>
@@ -1312,13 +1312,13 @@
         <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.2938</v>
+        <v>-0.1789</v>
       </c>
       <c r="T11" t="n">
-        <v>0.311</v>
+        <v>0.3715</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.6048</v>
+        <v>-0.5503</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8828</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.2861</v>
+        <v>-5.8756</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.3092</v>
+        <v>-1.8442</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9769</v>
+        <v>-4.0313</v>
       </c>
       <c r="G12" t="n">
         <v>-0.4352</v>
@@ -1390,13 +1390,13 @@
         <v>1.1721</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9058</v>
+        <v>-0.4952</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.3961</v>
+        <v>0.0689</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5096000000000001</v>
+        <v>-0.5641</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9917</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.9091</v>
+        <v>-19.3041</v>
       </c>
       <c r="E13" t="n">
-        <v>-5.3046</v>
+        <v>-4.699400000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.6045</v>
+        <v>-14.6047</v>
       </c>
       <c r="G13" t="n">
         <v>-5.418099999999999</v>
@@ -1468,19 +1468,19 @@
         <v>12.6973</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.9524</v>
+        <v>-4.347099999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1501999999999997</v>
+        <v>0.4550000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.8021</v>
+        <v>-4.802</v>
       </c>
       <c r="V13" t="n">
         <v>-4.6551</v>
       </c>
       <c r="W13" t="n">
-        <v>1.995299999999999</v>
+        <v>1.9953</v>
       </c>
       <c r="X13" t="n">
         <v>-6.650399999999999</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.531000000000001</v>
+        <v>8.7798</v>
       </c>
       <c r="E14" t="n">
-        <v>7.2539</v>
+        <v>7.5572</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2771</v>
+        <v>1.2226</v>
       </c>
       <c r="G14" t="n">
         <v>4.8678</v>
@@ -1546,13 +1546,13 @@
         <v>2.5395</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.427</v>
+        <v>-0.1781</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.4099</v>
+        <v>-0.1065</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0171</v>
+        <v>-0.0716</v>
       </c>
       <c r="V14" t="n">
         <v>1.5507</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.8176</v>
+        <v>6.7332</v>
       </c>
       <c r="E15" t="n">
         <v>4.9044</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9132</v>
+        <v>1.8288</v>
       </c>
       <c r="G15" t="n">
         <v>3.1691</v>
@@ -1624,13 +1624,13 @@
         <v>2.3441</v>
       </c>
       <c r="S15" t="n">
-        <v>1.0625</v>
+        <v>0.9781</v>
       </c>
       <c r="T15" t="n">
         <v>0.5752</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4873</v>
+        <v>0.4029</v>
       </c>
       <c r="V15" t="n">
         <v>1.2186</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.3563</v>
+        <v>4.9639</v>
       </c>
       <c r="E16" t="n">
-        <v>2.6789</v>
+        <v>3.6901</v>
       </c>
       <c r="F16" t="n">
-        <v>0.6774</v>
+        <v>1.2738</v>
       </c>
       <c r="G16" t="n">
         <v>3.0176</v>
@@ -1702,13 +1702,13 @@
         <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.6845</v>
+        <v>0.9231</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.652</v>
+        <v>0.3592</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0326</v>
+        <v>0.5639</v>
       </c>
       <c r="V16" t="n">
         <v>1.2186</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>Q. BARDÉS BADIA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.3086</v>
+        <v>2.2406</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9213</v>
+        <v>0.9523</v>
       </c>
       <c r="F17" t="n">
-        <v>0.3873</v>
+        <v>1.2882</v>
       </c>
       <c r="G17" t="n">
-        <v>1.1981</v>
+        <v>1.5273</v>
       </c>
       <c r="H17" t="n">
-        <v>0.1059</v>
+        <v>0.9883</v>
       </c>
       <c r="I17" t="n">
-        <v>1.0922</v>
+        <v>0.5391</v>
       </c>
       <c r="J17" t="n">
-        <v>2.3661</v>
+        <v>1.2075</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6782</v>
+        <v>1.2075</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.168</v>
+        <v>0.3199</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.5723</v>
+        <v>-0.2192</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4043</v>
+        <v>0.5391</v>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S17" t="n">
-        <v>1.1105</v>
+        <v>0.1272</v>
       </c>
       <c r="T17" t="n">
-        <v>1.0594</v>
+        <v>-0.0598</v>
       </c>
       <c r="U17" t="n">
-        <v>0.0511</v>
+        <v>0.187</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.3321</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.0462</v>
+        <v>1.8302</v>
       </c>
       <c r="E18" t="n">
-        <v>0.649</v>
+        <v>1.4158</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3972</v>
+        <v>0.4145</v>
       </c>
       <c r="G18" t="n">
-        <v>1.5273</v>
+        <v>1.1981</v>
       </c>
       <c r="H18" t="n">
-        <v>0.9883</v>
+        <v>0.1059</v>
       </c>
       <c r="I18" t="n">
-        <v>0.5391</v>
+        <v>1.0922</v>
       </c>
       <c r="J18" t="n">
-        <v>1.2075</v>
+        <v>2.3661</v>
       </c>
       <c r="K18" t="n">
-        <v>1.2075</v>
+        <v>1.6782</v>
       </c>
       <c r="L18" t="n">
+        <v>0.6879</v>
+      </c>
+      <c r="M18" t="n">
+        <v>-1.168</v>
+      </c>
+      <c r="N18" t="n">
+        <v>-1.5723</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="n">
-        <v>0.3199</v>
-      </c>
-      <c r="N18" t="n">
-        <v>-0.2192</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0.5391</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0.586</v>
-      </c>
       <c r="Q18" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>1.1721</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0672</v>
+        <v>0.6322</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3631</v>
+        <v>0.5538</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2959</v>
+        <v>0.0784</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.3321</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.7102</v>
+        <v>1.6011</v>
       </c>
       <c r="E19" t="n">
-        <v>2.4928</v>
+        <v>0.8112</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.7826</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.0315</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5165</v>
+        <v>-0.0156</v>
       </c>
       <c r="I19" t="n">
-        <v>0.485</v>
+        <v>0.6603</v>
       </c>
       <c r="J19" t="n">
-        <v>1.1464</v>
+        <v>1.8226</v>
       </c>
       <c r="K19" t="n">
-        <v>1.0655</v>
+        <v>1.7012</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0809</v>
+        <v>0.1214</v>
       </c>
       <c r="M19" t="n">
         <v>-1.1779</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.582</v>
+        <v>-1.7168</v>
       </c>
       <c r="O19" t="n">
-        <v>0.4041</v>
+        <v>0.5389</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q19" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5193</v>
+        <v>0.4485</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4914</v>
+        <v>0.3523</v>
       </c>
       <c r="U19" t="n">
-        <v>0.028</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2224</v>
+        <v>-0.6642</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8317</v>
+        <v>-0.3869</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.5725</v>
+        <v>1.3265</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2157</v>
+        <v>1.785</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3568</v>
+        <v>-0.4584</v>
       </c>
       <c r="G20" t="n">
-        <v>0.6447000000000001</v>
+        <v>-0.0315</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0156</v>
+        <v>-0.5165</v>
       </c>
       <c r="I20" t="n">
-        <v>0.6603</v>
+        <v>0.485</v>
       </c>
       <c r="J20" t="n">
-        <v>1.8226</v>
+        <v>1.1464</v>
       </c>
       <c r="K20" t="n">
-        <v>1.7012</v>
+        <v>1.0655</v>
       </c>
       <c r="L20" t="n">
-        <v>0.1214</v>
+        <v>0.0809</v>
       </c>
       <c r="M20" t="n">
         <v>-1.1779</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.7168</v>
+        <v>-1.582</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5389</v>
+        <v>0.4041</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>2.1488</v>
+        <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.4199</v>
+        <v>1.1356</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7567</v>
+        <v>0.7836</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3368</v>
+        <v>0.3521</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.6642</v>
+        <v>0.2224</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3869</v>
+        <v>0.8317</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.2772</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2192</v>
+        <v>1.1967</v>
       </c>
       <c r="E21" t="n">
-        <v>0.8381</v>
+        <v>1.5459</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6189</v>
+        <v>-0.3493</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7898</v>
@@ -2092,13 +2092,13 @@
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>0.154</v>
+        <v>1.1315</v>
       </c>
       <c r="T21" t="n">
-        <v>0.0221</v>
+        <v>0.7299</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1319</v>
+        <v>0.4015</v>
       </c>
       <c r="V21" t="n">
         <v>2.0503</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.7927</v>
+        <v>-1.4927</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4359</v>
+        <v>-2.2448</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6432</v>
+        <v>0.7522</v>
       </c>
       <c r="G22" t="n">
         <v>0.0286</v>
@@ -2170,13 +2170,13 @@
         <v>2.3441</v>
       </c>
       <c r="S22" t="n">
-        <v>1.1787</v>
+        <v>0.4788</v>
       </c>
       <c r="T22" t="n">
-        <v>1.5519</v>
+        <v>0.743</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.3732</v>
+        <v>-0.2642</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2186</v>
@@ -2203,10 +2203,10 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2273</v>
+        <v>-1.9351</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5994</v>
+        <v>-1.3072</v>
       </c>
       <c r="F23" t="n">
         <v>-0.6279</v>
@@ -2248,10 +2248,10 @@
         <v>0.3907</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2272</v>
+        <v>0.5193</v>
       </c>
       <c r="T23" t="n">
-        <v>1.362</v>
+        <v>0.6542</v>
       </c>
       <c r="U23" t="n">
         <v>-0.1348</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.6323</v>
+        <v>-3.9868</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.0956</v>
+        <v>-3.2867</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.5368000000000001</v>
+        <v>-0.7002</v>
       </c>
       <c r="G24" t="n">
         <v>-4.3686</v>
@@ -2326,13 +2326,13 @@
         <v>2.1488</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5409</v>
+        <v>0.1046</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.5915</v>
+        <v>0.2175</v>
       </c>
       <c r="U24" t="n">
-        <v>0.0505</v>
+        <v>-0.1129</v>
       </c>
       <c r="V24" t="n">
         <v>0.2772</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>19.9093</v>
+        <v>21.2574</v>
       </c>
       <c r="E25" t="n">
         <v>15.8232</v>
       </c>
       <c r="F25" t="n">
-        <v>4.085999999999999</v>
+        <v>5.434100000000001</v>
       </c>
       <c r="G25" t="n">
         <v>5.4181</v>
@@ -2404,13 +2404,13 @@
         <v>17.581</v>
       </c>
       <c r="S25" t="n">
-        <v>4.952500000000001</v>
+        <v>6.3008</v>
       </c>
       <c r="T25" t="n">
-        <v>4.8022</v>
+        <v>4.8024</v>
       </c>
       <c r="U25" t="n">
-        <v>0.1502000000000001</v>
+        <v>1.4985</v>
       </c>
       <c r="V25" t="n">
         <v>4.654999999999998</v>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484264_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484264_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -558,7 +563,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -626,17 +631,22 @@
       </c>
       <c r="X2" t="n">
         <v>-0.4996</v>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R. PALOMARES MUÑOZ</t>
+          <t>R. PALOMARES MUNOZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C3" t="n">
@@ -704,6 +714,11 @@
       </c>
       <c r="X3" t="n">
         <v>0.6642</v>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -714,7 +729,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C4" t="n">
@@ -782,792 +797,843 @@
       </c>
       <c r="X4" t="n">
         <v>-0.6093</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>E. MARTÍN GASCÓN</t>
+          <t>P. GONZÁLEZ BRUMOS</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.9655</v>
+        <v>0.614</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.7673</v>
+        <v>0.614</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1981</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.3002</v>
+        <v>0.614</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2215</v>
+        <v>0.614</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.5217</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9969</v>
+        <v>0.614</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9849</v>
+        <v>0.614</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.9818</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.3032</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7634</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.5399</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1721</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.216</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.183</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.399</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.5507</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. LLORENTE GUILLEMI</t>
+          <t>E. MARTIN GASCON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.6989</v>
+        <v>-0.9655</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2</v>
+        <v>-0.7673</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.499</v>
+        <v>-0.1981</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.0208</v>
+        <v>-2.3002</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.252</v>
+        <v>0.2215</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.7688</v>
+        <v>-2.5217</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8575</v>
+        <v>-0.9969</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.2239</v>
+        <v>0.9849</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.9818</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.1634</v>
+        <v>-1.3032</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0281</v>
+        <v>-0.7634</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.1352</v>
+        <v>-0.5399</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.586</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>-1.1721</v>
       </c>
       <c r="R6" t="n">
-        <v>0.586</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>0.5173</v>
+        <v>-0.216</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8296</v>
+        <v>0.183</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3123</v>
+        <v>-0.399</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.6093</v>
+        <v>1.5507</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6093</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ DIAZ</t>
+          <t>J. LLORENTE GUILLEMI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7238</v>
+        <v>-2.6989</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4923</v>
+        <v>-1.2</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.2315</v>
+        <v>-1.499</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5175999999999999</v>
+        <v>-2.0208</v>
       </c>
       <c r="H7" t="n">
-        <v>1.8286</v>
+        <v>-1.252</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.3462</v>
+        <v>-0.7688</v>
       </c>
       <c r="J7" t="n">
-        <v>0.6603</v>
+        <v>-0.8575</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2758</v>
+        <v>-0.2239</v>
       </c>
       <c r="L7" t="n">
-        <v>-2.6155</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.1779</v>
+        <v>-1.1634</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4472</v>
+        <v>-1.0281</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2692</v>
+        <v>-0.1352</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="R7" t="n">
-        <v>1.1721</v>
+        <v>0.586</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0228</v>
+        <v>0.5173</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.6252</v>
+        <v>0.8296</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3977</v>
+        <v>-0.3123</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.16</v>
+        <v>-0.6093</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.8279</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>F. ALVAREZ BACO</t>
+          <t>R. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C8" t="n">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.1221</v>
+        <v>-2.7238</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.7128</v>
+        <v>-0.4923</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.4094</v>
+        <v>-2.2315</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.5712</v>
+        <v>-0.5175999999999999</v>
       </c>
       <c r="H8" t="n">
-        <v>-3.8665</v>
+        <v>1.8286</v>
       </c>
       <c r="I8" t="n">
-        <v>1.2953</v>
+        <v>-2.3462</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.5099</v>
+        <v>0.6603</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.6706</v>
+        <v>3.2758</v>
       </c>
       <c r="L8" t="n">
-        <v>1.1607</v>
+        <v>-2.6155</v>
       </c>
       <c r="M8" t="n">
-        <v>-2.0613</v>
+        <v>-1.1779</v>
       </c>
       <c r="N8" t="n">
-        <v>-2.196</v>
+        <v>-1.4472</v>
       </c>
       <c r="O8" t="n">
-        <v>0.1346</v>
+        <v>0.2692</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9767</v>
+        <v>0.9767</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9767</v>
+        <v>1.1721</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1486</v>
+        <v>-1.0228</v>
       </c>
       <c r="T8" t="n">
-        <v>0.4733</v>
+        <v>-0.6252</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3247</v>
+        <v>-0.3977</v>
       </c>
       <c r="V8" t="n">
-        <v>0.2772</v>
+        <v>-2.16</v>
       </c>
       <c r="W8" t="n">
-        <v>0.2772</v>
+        <v>-0.3321</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.8279</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. LOZANO MASSANET</t>
+          <t>F. ALVAREZ BACO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C9" t="n">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.1589</v>
+        <v>-3.1221</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.0321</v>
+        <v>-1.7128</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1268</v>
+        <v>-1.4094</v>
       </c>
       <c r="G9" t="n">
-        <v>0.3395</v>
+        <v>-2.5712</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3525</v>
+        <v>-3.8665</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.013</v>
+        <v>1.2953</v>
       </c>
       <c r="J9" t="n">
-        <v>1.462</v>
+        <v>-0.5099</v>
       </c>
       <c r="K9" t="n">
-        <v>2.1489</v>
+        <v>-1.6706</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6869</v>
+        <v>1.1607</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.1225</v>
+        <v>-2.0613</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.7964</v>
+        <v>-2.196</v>
       </c>
       <c r="O9" t="n">
-        <v>0.6739000000000001</v>
+        <v>0.1346</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.3674</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.9301</v>
+        <v>-1.9534</v>
       </c>
       <c r="R9" t="n">
-        <v>1.5627</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.5765</v>
+        <v>0.1486</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.5639</v>
+        <v>0.4733</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.0126</v>
+        <v>-0.3247</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.5545</v>
+        <v>0.2772</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>V. MANDIM SILVA</t>
+          <t>G. LOZANO MASSANET</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C10" t="n">
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4826</v>
+        <v>-3.1589</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.1981</v>
+        <v>-2.0321</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.2845</v>
+        <v>-1.1268</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8857</v>
+        <v>0.3395</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.9258</v>
+        <v>0.3525</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0401</v>
+        <v>-0.013</v>
       </c>
       <c r="J10" t="n">
-        <v>0.492</v>
+        <v>1.462</v>
       </c>
       <c r="K10" t="n">
-        <v>0.4515</v>
+        <v>2.1489</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0405</v>
+        <v>-0.6869</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.3777</v>
+        <v>-1.1225</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.3773</v>
+        <v>-1.7964</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0004</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P10" t="n">
-        <v>-2.5395</v>
+        <v>-1.3674</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1255</v>
+        <v>-2.9301</v>
       </c>
       <c r="R10" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7216</v>
+        <v>-1.5765</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5646</v>
+        <v>-0.5639</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1569</v>
+        <v>-1.0126</v>
       </c>
       <c r="V10" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0.6642</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R. DALET CASALPRIM</t>
+          <t>V. MANDIM SILVA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C11" t="n">
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.234</v>
+        <v>-3.4826</v>
       </c>
       <c r="E11" t="n">
-        <v>-2.5478</v>
+        <v>-3.1981</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.6862</v>
+        <v>-0.2845</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.977</v>
+        <v>-0.8857</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.6529</v>
+        <v>-0.9258</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3241</v>
+        <v>0.0401</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0831</v>
+        <v>0.492</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.164</v>
+        <v>0.4515</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0809</v>
+        <v>0.0405</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.8939</v>
+        <v>-1.3777</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.4889</v>
+        <v>-1.3773</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.4051</v>
+        <v>-0.0004</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.1953</v>
+        <v>-2.5395</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1721</v>
+        <v>-3.1255</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.1789</v>
+        <v>-0.7216</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3715</v>
+        <v>-0.5646</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5503</v>
+        <v>-0.1569</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.8828</v>
+        <v>0.6642</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2186</v>
+        <v>0.6642</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>P. GONZÁLEZ BRUMOS</t>
+          <t>R. DALET CASALPRIM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.8756</v>
+        <v>-4.234</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.8442</v>
+        <v>-2.5478</v>
       </c>
       <c r="F12" t="n">
-        <v>-4.0313</v>
+        <v>-1.6862</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4352</v>
+        <v>-1.977</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3142</v>
+        <v>-1.6529</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.121</v>
+        <v>-0.3241</v>
       </c>
       <c r="J12" t="n">
-        <v>1.2124</v>
+        <v>-1.0831</v>
       </c>
       <c r="K12" t="n">
-        <v>1.3328</v>
+        <v>-1.164</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.1204</v>
+        <v>0.0809</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.6476</v>
+        <v>-0.8939</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.647</v>
+        <v>-0.4889</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.4051</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.9534</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.1255</v>
+        <v>-1.1721</v>
       </c>
       <c r="R12" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.4952</v>
+        <v>-0.1789</v>
       </c>
       <c r="T12" t="n">
-        <v>0.0689</v>
+        <v>0.3715</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.5641</v>
+        <v>-0.5503</v>
       </c>
       <c r="V12" t="n">
-        <v>-2.9917</v>
+        <v>-1.8828</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>-0.6642</v>
       </c>
       <c r="X12" t="n">
-        <v>-2.9917</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>P. GONZALEZ BRUMOS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SANDA ELECTROCLIMA TECLA SALA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C13" t="n">
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-19.3041</v>
+        <v>-6.4895</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.699400000000001</v>
+        <v>-2.4582</v>
       </c>
       <c r="F13" t="n">
-        <v>-14.6047</v>
+        <v>-4.0313</v>
       </c>
       <c r="G13" t="n">
-        <v>-5.418099999999999</v>
+        <v>-1.0491</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.0467</v>
+        <v>-0.9281</v>
       </c>
       <c r="I13" t="n">
-        <v>-3.371300000000001</v>
+        <v>-0.121</v>
       </c>
       <c r="J13" t="n">
-        <v>10.4311</v>
+        <v>0.5984</v>
       </c>
       <c r="K13" t="n">
-        <v>14.4716</v>
+        <v>0.7188</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0406</v>
+        <v>-0.1204</v>
       </c>
       <c r="M13" t="n">
-        <v>-15.849</v>
+        <v>-1.6476</v>
       </c>
       <c r="N13" t="n">
-        <v>-16.5183</v>
+        <v>-1.647</v>
       </c>
       <c r="O13" t="n">
-        <v>0.6689999999999999</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="P13" t="n">
-        <v>-4.883599999999999</v>
+        <v>-1.9534</v>
       </c>
       <c r="Q13" t="n">
-        <v>-17.5809</v>
+        <v>-3.1255</v>
       </c>
       <c r="R13" t="n">
-        <v>12.6973</v>
+        <v>1.1721</v>
       </c>
       <c r="S13" t="n">
-        <v>-4.347099999999999</v>
+        <v>-0.4952</v>
       </c>
       <c r="T13" t="n">
-        <v>0.4550000000000001</v>
+        <v>0.0689</v>
       </c>
       <c r="U13" t="n">
-        <v>-4.802</v>
+        <v>-0.5641</v>
       </c>
       <c r="V13" t="n">
-        <v>-4.6551</v>
+        <v>-2.9917</v>
       </c>
       <c r="W13" t="n">
-        <v>1.9953</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.650399999999999</v>
+        <v>-2.9917</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>D. ROY CARNICER</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>TENEA-C.B. ESPARREGUERA</t>
+          <t>SANDÁ ELECTROCLIMA - BC TECLA SALA  A</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>8.7798</v>
+        <v>-19.304</v>
       </c>
       <c r="E14" t="n">
-        <v>7.5572</v>
+        <v>-4.699400000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>1.2226</v>
+        <v>-14.6047</v>
       </c>
       <c r="G14" t="n">
-        <v>4.8678</v>
+        <v>-5.418</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6035</v>
+        <v>-2.0466</v>
       </c>
       <c r="I14" t="n">
-        <v>3.2643</v>
+        <v>-3.3713</v>
       </c>
       <c r="J14" t="n">
-        <v>6.4451</v>
+        <v>10.4311</v>
       </c>
       <c r="K14" t="n">
-        <v>3.3154</v>
+        <v>14.4716</v>
       </c>
       <c r="L14" t="n">
-        <v>3.1297</v>
+        <v>-4.0406</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.5773</v>
+        <v>-15.849</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.712</v>
+        <v>-16.5183</v>
       </c>
       <c r="O14" t="n">
-        <v>0.1346</v>
+        <v>0.6689999999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>2.5395</v>
+        <v>-4.883599999999999</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-17.5809</v>
       </c>
       <c r="R14" t="n">
-        <v>2.5395</v>
+        <v>12.6973</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.1781</v>
+        <v>-4.347099999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.1065</v>
+        <v>0.4550000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.0716</v>
+        <v>-4.802</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5507</v>
+        <v>-4.6551</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2186</v>
+        <v>1.9953</v>
       </c>
       <c r="X14" t="n">
-        <v>0.3321</v>
-      </c>
+        <v>-6.650399999999999</v>
+      </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. SEGARRA BAQUES</t>
+          <t>D. ROY CARNICER</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1645,78 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.7332</v>
+        <v>8.7798</v>
       </c>
       <c r="E15" t="n">
-        <v>4.9044</v>
+        <v>7.5572</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8288</v>
+        <v>1.2226</v>
       </c>
       <c r="G15" t="n">
-        <v>3.1691</v>
+        <v>4.8678</v>
       </c>
       <c r="H15" t="n">
-        <v>2.711</v>
+        <v>1.6035</v>
       </c>
       <c r="I15" t="n">
-        <v>0.4582</v>
+        <v>3.2643</v>
       </c>
       <c r="J15" t="n">
-        <v>4.0873</v>
+        <v>6.4451</v>
       </c>
       <c r="K15" t="n">
-        <v>4.033</v>
+        <v>3.3154</v>
       </c>
       <c r="L15" t="n">
-        <v>0.0543</v>
+        <v>3.1297</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.9182</v>
+        <v>-1.5773</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.3221</v>
+        <v>-1.712</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4039</v>
+        <v>0.1346</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3674</v>
+        <v>2.5395</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>2.3441</v>
+        <v>2.5395</v>
       </c>
       <c r="S15" t="n">
-        <v>0.9781</v>
+        <v>-0.1781</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5752</v>
+        <v>-0.1065</v>
       </c>
       <c r="U15" t="n">
-        <v>0.4029</v>
+        <v>-0.0716</v>
       </c>
       <c r="V15" t="n">
-        <v>1.2186</v>
+        <v>1.5507</v>
       </c>
       <c r="W15" t="n">
         <v>1.2186</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. MARTIN TRENADO</t>
+          <t>M. SEGARRA BAQUES</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,58 +1728,58 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>4.9639</v>
+        <v>6.7332</v>
       </c>
       <c r="E16" t="n">
-        <v>3.6901</v>
+        <v>4.9044</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2738</v>
+        <v>1.8288</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0176</v>
+        <v>3.1691</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2886</v>
+        <v>2.711</v>
       </c>
       <c r="I16" t="n">
-        <v>0.729</v>
+        <v>0.4582</v>
       </c>
       <c r="J16" t="n">
-        <v>4.0657</v>
+        <v>4.0873</v>
       </c>
       <c r="K16" t="n">
-        <v>3.6058</v>
+        <v>4.033</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4599</v>
+        <v>0.0543</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.0482</v>
+        <v>-0.9182</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.3172</v>
+        <v>-1.3221</v>
       </c>
       <c r="O16" t="n">
-        <v>0.269</v>
+        <v>0.4039</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.1953</v>
+        <v>1.3674</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R16" t="n">
-        <v>1.7581</v>
+        <v>2.3441</v>
       </c>
       <c r="S16" t="n">
-        <v>0.9231</v>
+        <v>0.9781</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3592</v>
+        <v>0.5752</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5639</v>
+        <v>0.4029</v>
       </c>
       <c r="V16" t="n">
         <v>1.2186</v>
@@ -1718,12 +1789,17 @@
       </c>
       <c r="X16" t="n">
         <v>0</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Q. BARDÉS BADIA</t>
+          <t>J. MARTIN TRENADO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.2406</v>
+        <v>4.9639</v>
       </c>
       <c r="E17" t="n">
-        <v>0.9523</v>
+        <v>3.6901</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2882</v>
+        <v>1.2738</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5273</v>
+        <v>3.0176</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9883</v>
+        <v>2.2886</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5391</v>
+        <v>0.729</v>
       </c>
       <c r="J17" t="n">
-        <v>1.2075</v>
+        <v>4.0657</v>
       </c>
       <c r="K17" t="n">
-        <v>1.2075</v>
+        <v>3.6058</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.4599</v>
       </c>
       <c r="M17" t="n">
-        <v>0.3199</v>
+        <v>-1.0482</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.2192</v>
+        <v>-1.3172</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5391</v>
+        <v>0.269</v>
       </c>
       <c r="P17" t="n">
-        <v>0.586</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.1953</v>
+        <v>-1.9534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.7814</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>0.1272</v>
+        <v>0.9231</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.0598</v>
+        <v>0.3592</v>
       </c>
       <c r="U17" t="n">
-        <v>0.187</v>
+        <v>0.5639</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>X. ALMIRALL CANALS</t>
+          <t>Q. BARDES BADIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.8302</v>
+        <v>2.2406</v>
       </c>
       <c r="E18" t="n">
-        <v>1.4158</v>
+        <v>0.9523</v>
       </c>
       <c r="F18" t="n">
-        <v>0.4145</v>
+        <v>1.2882</v>
       </c>
       <c r="G18" t="n">
-        <v>1.1981</v>
+        <v>1.5273</v>
       </c>
       <c r="H18" t="n">
-        <v>0.1059</v>
+        <v>0.9883</v>
       </c>
       <c r="I18" t="n">
-        <v>1.0922</v>
+        <v>0.5391</v>
       </c>
       <c r="J18" t="n">
-        <v>2.3661</v>
+        <v>1.2075</v>
       </c>
       <c r="K18" t="n">
-        <v>1.6782</v>
+        <v>1.2075</v>
       </c>
       <c r="L18" t="n">
-        <v>0.6879</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.168</v>
+        <v>0.3199</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.5723</v>
+        <v>-0.2192</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4043</v>
+        <v>0.5391</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1721</v>
+        <v>-0.1953</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1721</v>
+        <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6322</v>
+        <v>0.1272</v>
       </c>
       <c r="T18" t="n">
-        <v>0.5538</v>
+        <v>-0.0598</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0784</v>
+        <v>0.187</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>0.3321</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. ESTEVES-GARCIA COFFI</t>
+          <t>X. ALMIRALL CANALS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.6011</v>
+        <v>1.8302</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8112</v>
+        <v>1.4158</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7897999999999999</v>
+        <v>0.4145</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6447000000000001</v>
+        <v>1.1981</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0156</v>
+        <v>0.1059</v>
       </c>
       <c r="I19" t="n">
-        <v>0.6603</v>
+        <v>1.0922</v>
       </c>
       <c r="J19" t="n">
-        <v>1.8226</v>
+        <v>2.3661</v>
       </c>
       <c r="K19" t="n">
-        <v>1.7012</v>
+        <v>1.6782</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1214</v>
+        <v>0.6879</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1779</v>
+        <v>-1.168</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.7168</v>
+        <v>-1.5723</v>
       </c>
       <c r="O19" t="n">
-        <v>0.5389</v>
+        <v>0.4043</v>
       </c>
       <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-1.1721</v>
+      </c>
+      <c r="R19" t="n">
         <v>1.1721</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-0.9767</v>
-      </c>
-      <c r="R19" t="n">
-        <v>2.1488</v>
-      </c>
       <c r="S19" t="n">
-        <v>0.4485</v>
+        <v>0.6322</v>
       </c>
       <c r="T19" t="n">
-        <v>0.3523</v>
+        <v>0.5538</v>
       </c>
       <c r="U19" t="n">
-        <v>0.09619999999999999</v>
+        <v>0.0784</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>-0.3869</v>
+        <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.2772</v>
+        <v>0.3321</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>J. SOLE PIE</t>
+          <t>S. ESTEVES-GARCIA COFFI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +2060,78 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>1.3265</v>
+        <v>1.6011</v>
       </c>
       <c r="E20" t="n">
-        <v>1.785</v>
+        <v>0.8112</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.4584</v>
+        <v>0.7897999999999999</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.0315</v>
+        <v>0.6447000000000001</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5165</v>
+        <v>-0.0156</v>
       </c>
       <c r="I20" t="n">
-        <v>0.485</v>
+        <v>0.6603</v>
       </c>
       <c r="J20" t="n">
-        <v>1.1464</v>
+        <v>1.8226</v>
       </c>
       <c r="K20" t="n">
-        <v>1.0655</v>
+        <v>1.7012</v>
       </c>
       <c r="L20" t="n">
-        <v>0.0809</v>
+        <v>0.1214</v>
       </c>
       <c r="M20" t="n">
         <v>-1.1779</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.582</v>
+        <v>-1.7168</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4041</v>
+        <v>0.5389</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>1.1721</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>2.1488</v>
       </c>
       <c r="S20" t="n">
-        <v>1.1356</v>
+        <v>0.4485</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7836</v>
+        <v>0.3523</v>
       </c>
       <c r="U20" t="n">
-        <v>0.3521</v>
+        <v>0.09619999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>0.2224</v>
+        <v>-0.6642</v>
       </c>
       <c r="W20" t="n">
-        <v>0.8317</v>
+        <v>-0.3869</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6093</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. CAMPAÑA SOLER</t>
+          <t>J. SOLE PIE</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>1.1967</v>
+        <v>1.3265</v>
       </c>
       <c r="E21" t="n">
-        <v>1.5459</v>
+        <v>1.785</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.3493</v>
+        <v>-0.4584</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7898</v>
+        <v>-0.0315</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4815</v>
+        <v>-0.5165</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.3083</v>
+        <v>0.485</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.2809</v>
+        <v>1.1464</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7009</v>
+        <v>1.0655</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.9818</v>
+        <v>0.0809</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.5089</v>
+        <v>-1.1779</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.1824</v>
+        <v>-1.582</v>
       </c>
       <c r="O21" t="n">
-        <v>0.6735</v>
+        <v>0.4041</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
         <v>0.9767</v>
       </c>
       <c r="S21" t="n">
-        <v>1.1315</v>
+        <v>1.1356</v>
       </c>
       <c r="T21" t="n">
-        <v>0.7299</v>
+        <v>0.7836</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4015</v>
+        <v>0.3521</v>
       </c>
       <c r="V21" t="n">
-        <v>2.0503</v>
+        <v>0.2224</v>
       </c>
       <c r="W21" t="n">
-        <v>3.269</v>
+        <v>0.8317</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. ROSADO FORNIES</t>
+          <t>P. CAMPAÑA SOLER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.4927</v>
+        <v>0.614</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2448</v>
+        <v>0.614</v>
       </c>
       <c r="F22" t="n">
-        <v>0.7522</v>
+        <v>0</v>
       </c>
       <c r="G22" t="n">
-        <v>0.0286</v>
+        <v>0.614</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7667</v>
+        <v>0.614</v>
       </c>
       <c r="I22" t="n">
-        <v>0.7953</v>
+        <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0.8018</v>
+        <v>0.614</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6804</v>
+        <v>0.614</v>
       </c>
       <c r="L22" t="n">
-        <v>0.1214</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.7733</v>
+        <v>0</v>
       </c>
       <c r="N22" t="n">
-        <v>-1.4472</v>
+        <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>0.6739000000000001</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-3.1255</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.3441</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.4788</v>
+        <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0.743</v>
+        <v>0</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2642</v>
+        <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6642</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>S. ROMEO FO</t>
+          <t>P. CAMPANA SOLER</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.9351</v>
+        <v>0.5827</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.3072</v>
+        <v>0.9319</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6279</v>
+        <v>-0.3493</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8452</v>
+        <v>-2.4038</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9417</v>
+        <v>-1.0954</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.9035</v>
+        <v>-1.3083</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.9614</v>
+        <v>-1.8949</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.3277</v>
+        <v>0.08690000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.9818</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.8838</v>
+        <v>-0.5089</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.614</v>
+        <v>-1.1824</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2698</v>
+        <v>0.6735</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>-1.1721</v>
       </c>
       <c r="R23" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>0.5193</v>
+        <v>1.1315</v>
       </c>
       <c r="T23" t="n">
-        <v>0.6542</v>
+        <v>0.7299</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1348</v>
+        <v>0.4015</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>2.0503</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>3.269</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>A. BARQUETS ARIZA</t>
+          <t>M. ROSADO FORNIES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,73 +2392,78 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.9868</v>
+        <v>-1.4927</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.2867</v>
+        <v>-2.2448</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.7002</v>
+        <v>0.7522</v>
       </c>
       <c r="G24" t="n">
-        <v>-4.3686</v>
+        <v>0.0286</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.9286</v>
+        <v>-0.7667</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.44</v>
+        <v>0.7953</v>
       </c>
       <c r="J24" t="n">
-        <v>-2.8512</v>
+        <v>0.8018</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.142</v>
+        <v>0.6804</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.7092</v>
+        <v>0.1214</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.5174</v>
+        <v>-0.7733</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.7866</v>
+        <v>-1.4472</v>
       </c>
       <c r="O24" t="n">
-        <v>0.2692</v>
+        <v>0.6739000000000001</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-0.7814</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.1488</v>
+        <v>-3.1255</v>
       </c>
       <c r="R24" t="n">
-        <v>2.1488</v>
+        <v>2.3441</v>
       </c>
       <c r="S24" t="n">
-        <v>0.1046</v>
+        <v>0.4788</v>
       </c>
       <c r="T24" t="n">
-        <v>0.2175</v>
+        <v>0.743</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1129</v>
+        <v>-0.2642</v>
       </c>
       <c r="V24" t="n">
-        <v>0.2772</v>
+        <v>-1.2186</v>
       </c>
       <c r="W24" t="n">
-        <v>1.4959</v>
+        <v>-0.6642</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.2186</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>S. ROMEO FO</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,68 +2475,235 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
+        <v>-1.9351</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-1.3072</v>
+      </c>
+      <c r="F25" t="n">
+        <v>-0.6279</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.8452</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-1.9417</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-0.9035</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-1.9614</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-1.3277</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-0.6336000000000001</v>
+      </c>
+      <c r="M25" t="n">
+        <v>-0.8838</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.614</v>
+      </c>
+      <c r="O25" t="n">
+        <v>-0.2698</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>0</v>
+      </c>
+      <c r="R25" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="S25" t="n">
+        <v>0.5193</v>
+      </c>
+      <c r="T25" t="n">
+        <v>0.6542</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.1348</v>
+      </c>
+      <c r="V25" t="n">
+        <v>0</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0</v>
+      </c>
+      <c r="X25" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A. BARQUETS ARIZA</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-3.9868</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.2867</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.7002</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-4.3686</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-1.9286</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-2.8512</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-0.142</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-2.7092</v>
+      </c>
+      <c r="M26" t="n">
+        <v>-1.5174</v>
+      </c>
+      <c r="N26" t="n">
+        <v>-1.7866</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0.2692</v>
+      </c>
+      <c r="P26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-2.1488</v>
+      </c>
+      <c r="R26" t="n">
+        <v>2.1488</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0.1046</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0.2175</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.1129</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="W26" t="n">
+        <v>1.4959</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484264_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>TENEA-C.B. ESPARREGUERA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
         <v>21.2574</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E27" t="n">
         <v>15.8232</v>
       </c>
-      <c r="F25" t="n">
-        <v>5.434100000000001</v>
-      </c>
-      <c r="G25" t="n">
+      <c r="F27" t="n">
+        <v>5.4341</v>
+      </c>
+      <c r="G27" t="n">
         <v>5.4181</v>
       </c>
-      <c r="H25" t="n">
-        <v>2.0467</v>
-      </c>
-      <c r="I25" t="n">
+      <c r="H27" t="n">
+        <v>2.0468</v>
+      </c>
+      <c r="I27" t="n">
         <v>3.3716</v>
       </c>
-      <c r="J25" t="n">
+      <c r="J27" t="n">
         <v>15.849</v>
       </c>
-      <c r="K25" t="n">
+      <c r="K27" t="n">
         <v>16.5182</v>
       </c>
-      <c r="L25" t="n">
-        <v>-0.6690999999999998</v>
-      </c>
-      <c r="M25" t="n">
+      <c r="L27" t="n">
+        <v>-0.6690999999999994</v>
+      </c>
+      <c r="M27" t="n">
         <v>-10.431</v>
       </c>
-      <c r="N25" t="n">
+      <c r="N27" t="n">
         <v>-14.4718</v>
       </c>
-      <c r="O25" t="n">
+      <c r="O27" t="n">
         <v>4.040699999999999</v>
       </c>
-      <c r="P25" t="n">
+      <c r="P27" t="n">
         <v>4.8837</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="Q27" t="n">
         <v>-12.6973</v>
       </c>
-      <c r="R25" t="n">
+      <c r="R27" t="n">
         <v>17.581</v>
       </c>
-      <c r="S25" t="n">
-        <v>6.3008</v>
-      </c>
-      <c r="T25" t="n">
+      <c r="S27" t="n">
+        <v>6.300799999999999</v>
+      </c>
+      <c r="T27" t="n">
         <v>4.8024</v>
       </c>
-      <c r="U25" t="n">
+      <c r="U27" t="n">
         <v>1.4985</v>
       </c>
-      <c r="V25" t="n">
+      <c r="V27" t="n">
         <v>4.654999999999998</v>
       </c>
-      <c r="W25" t="n">
+      <c r="W27" t="n">
         <v>7.869199999999999</v>
       </c>
-      <c r="X25" t="n">
+      <c r="X27" t="n">
         <v>-3.214</v>
       </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
